--- a/ig/main/CodeSystem-tre-r404-mode-fonctionnement-activite-smsse-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r404-mode-fonctionnement-activite-smsse-regulee.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
